--- a/data/Excel/GuLiStrikeVfx.xlsx
+++ b/data/Excel/GuLiStrikeVfx.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -410,6 +410,33 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Buildings/Materials/M_BuildingPlacementPreview.M_BuildingPlacementPreview</t>
+  </si>
+  <si>
+    <t>BuildingConstructionHologram</t>
+  </si>
+  <si>
+    <t>未完工建筑蓝色透明虚影</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/M_ConstructionHologram.M_ConstructionHologram</t>
+  </si>
+  <si>
+    <t>BuildingConstructionFinish</t>
+  </si>
+  <si>
+    <t>建筑完工蓝白色边缘发光</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/M_ConstructionFinishGlow.M_ConstructionFinishGlow</t>
+  </si>
+  <si>
+    <t>BuildingPlacementGrid</t>
+  </si>
+  <si>
+    <t>建筑占地区域世界坐标一米网格</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/M_BuildingPlacementGrid.M_BuildingPlacementGrid</t>
   </si>
 </sst>
 </file>
@@ -1712,6 +1739,75 @@
         <v>1</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeVfx.xlsx
+++ b/data/Excel/GuLiStrikeVfx.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>id</t>
   </si>
@@ -437,6 +437,51 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Buildings/Construction/M_BuildingPlacementGrid.M_BuildingPlacementGrid</t>
+  </si>
+  <si>
+    <t>BuildingConstructionComplete</t>
+  </si>
+  <si>
+    <t>矿厂完工底部UpgradeGlow一次性完整闪光</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionComplete.NS_ConstructionComplete</t>
+  </si>
+  <si>
+    <t>BuildingConstructionTopLoop</t>
+  </si>
+  <si>
+    <t>矿厂屋檐淡青绿呼吸光柱、漂浮粒子与独立电火花</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionTopLoop.NS_ConstructionTopLoop</t>
+  </si>
+  <si>
+    <t>BuildingConstructionLaser</t>
+  </si>
+  <si>
+    <t>建造车左右紫色激光、蓝白落点火花</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionLaser_Purple.NS_ConstructionLaser_Purple</t>
+  </si>
+  <si>
+    <t>BuildingConstructionColumnTail</t>
+  </si>
+  <si>
+    <t>施工弱光柱材质，提取UpgradeGlow残尾</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/M_ConstructionColumnTail.M_ConstructionColumnTail</t>
+  </si>
+  <si>
+    <t>BuildingConstructionMote</t>
+  </si>
+  <si>
+    <t>施工向上漂浮三角粒子材质</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/M_ConstructionMote.M_ConstructionMote</t>
   </si>
 </sst>
 </file>
@@ -1808,6 +1853,121 @@
         <v>1</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeVfx.xlsx
+++ b/data/Excel/GuLiStrikeVfx.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t>id</t>
   </si>
@@ -482,6 +482,63 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Buildings/Construction/M_ConstructionMote.M_ConstructionMote</t>
+  </si>
+  <si>
+    <t>WarMachineHover</t>
+  </si>
+  <si>
+    <t>战争机器四盘蓝色喷流与世界空间余迹；1024喷口每批；独立180-200米淡出</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/WarMachineHover/NS_WarMachineHoverPool.NS_WarMachineHoverPool</t>
+  </si>
+  <si>
+    <t>重防号四盘蓝色喷流与世界空间余迹；1024喷口每批；独立180-200米淡出</t>
+  </si>
+  <si>
+    <t>WM01MissileClusterFull</t>
+  </si>
+  <si>
+    <t>重防号独立GPU集群；每批64枚；24段一秒历史拖尾</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/WM01Missiles/NS_WM01MissileCluster_Full.NS_WM01MissileCluster_Full</t>
+  </si>
+  <si>
+    <t>WM01MissileClusterLite</t>
+  </si>
+  <si>
+    <t>重防号独立GPU集群；每批64枚；8段低采样历史拖尾</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/WM01Missiles/NS_WM01MissileCluster_Lite.NS_WM01MissileCluster_Lite</t>
+  </si>
+  <si>
+    <t>WM01MissileClusterMinimal</t>
+  </si>
+  <si>
+    <t>重防号独立GPU集群；每批64枚；仅弹体与尾焰</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/WM01Missiles/NS_WM01MissileCluster_Minimal.NS_WM01MissileCluster_Minimal</t>
+  </si>
+  <si>
+    <t>重防号独立GPU候选；每批按实际占用分配且最多64枚；24段1.2秒历史烟迹</t>
+  </si>
+  <si>
+    <t>重防号独立GPU候选；每批最多64枚；8段1.2秒历史烟迹；0.15秒平滑交接</t>
+  </si>
+  <si>
+    <t>重防号独立GPU候选；每批最多64枚；仅弹体与短尾焰；保留旧档烟迹自然消散</t>
+  </si>
+  <si>
+    <t>重防号GPU候选v2；每批按实际占用分配且最多64枚；24段2.4秒浓黑烟迹；弹体/尾焰/烟宽为v1的1.5倍</t>
+  </si>
+  <si>
+    <t>重防号GPU候选v2；每批最多64枚；8段2.4秒浓黑烟迹；0.15秒平滑交接；旧烟迹自然消散</t>
+  </si>
+  <si>
+    <t>重防号GPU候选v2；每批最多64枚；仅1.5倍弹体与短尾焰；尾焰峰值3倍；保留旧档烟迹自然消散</t>
   </si>
 </sst>
 </file>
@@ -1968,6 +2025,98 @@
         <v>1</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeVfx.xlsx
+++ b/data/Excel/GuLiStrikeVfx.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -539,6 +539,18 @@
   </si>
   <si>
     <t>重防号GPU候选v2；每批最多64枚；仅1.5倍弹体与短尾焰；尾焰峰值3倍；保留旧档烟迹自然消散</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/GroundMech/NS_GroundMech_RocketJet.NS_GroundMech_RocketJet</t>
+  </si>
+  <si>
+    <t>重防号盘底喷焰与5–15米渐长拖尾；1024喷口每批；指挥官前两档显示，第三档总览隐藏</t>
+  </si>
+  <si>
+    <t>GroundMachineGunMuzzle</t>
+  </si>
+  <si>
+    <t>指挥官机械机枪枪口；保持基础尺寸，重防号在调用处乘2</t>
   </si>
 </sst>
 </file>
@@ -1050,13 +1062,13 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1162,7 +1174,7 @@
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2033,7 +2045,7 @@
         <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
         <v>158</v>
@@ -2117,6 +2129,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeVfx.xlsx
+++ b/data/Excel/GuLiStrikeVfx.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t>id</t>
   </si>
@@ -551,6 +551,96 @@
   </si>
   <si>
     <t>指挥官机械机枪枪口；保持基础尺寸，重防号在调用处乘2</t>
+  </si>
+  <si>
+    <t>采矿激光；建造使用独立 ID 45</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_Optimized.NS_MachineGunImpact_Optimized</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/Mining/NS_MiningLaser_Optimized.NS_MiningLaser_Optimized</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionLaser_Optimized.NS_ConstructionLaser_Optimized</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_Optimized.NS_MachineGunMuzzle_Optimized</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/WingmanWeapons/NS_WingmanLaserPool_SmallBatches.NS_WingmanLaserPool_SmallBatches</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_AllOptimizations.NS_MachineGunImpact_AllOptimizations</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/Mining/NS_MiningLaser_Optimized_GPU_All.NS_MiningLaser_Optimized_GPU_All</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionLaser_Optimized_GPU_All.NS_ConstructionLaser_Optimized_GPU_All</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_AllOptimizations.NS_MachineGunMuzzle_AllOptimizations</t>
+  </si>
+  <si>
+    <t>ReducedResourcePath</t>
+  </si>
+  <si>
+    <t>MinimalResourcePath</t>
+  </si>
+  <si>
+    <t>BatchResourcePath</t>
+  </si>
+  <si>
+    <t>ReducedBatchResourcePath</t>
+  </si>
+  <si>
+    <t>MinimalBatchResourcePath</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_AllOptimizations_Reduced.NS_MachineGunImpact_AllOptimizations_Reduced</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_AllOptimizations_Minimal.NS_MachineGunImpact_AllOptimizations_Minimal</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_Batch.NS_MachineGunImpact_Batch</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_Batch_Reduced.NS_MachineGunImpact_Batch_Reduced</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunImpact_Batch_Minimal.NS_MachineGunImpact_Batch_Minimal</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/Mining/NS_MiningLaser_Optimized_GPU_All_ThreeTier.NS_MiningLaser_Optimized_GPU_All_ThreeTier</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Buildings/Construction/NS_ConstructionLaser_Optimized_GPU_All_ThreeTier.NS_ConstructionLaser_Optimized_GPU_All_ThreeTier</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_AllOptimizations_Reduced.NS_MachineGunMuzzle_AllOptimizations_Reduced</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_AllOptimizations_Minimal.NS_MachineGunMuzzle_AllOptimizations_Minimal</t>
+  </si>
+  <si>
+    <t>WingmanGroundFlightBatch</t>
+  </si>
+  <si>
+    <t>僚机对地导弹独立不透明脉冲光点与实体尾迹；Profile专属，Scale=1</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_WingmanGroundFlight_SphereTrail.NS_WingmanGroundFlight_SphereTrail</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_Batch.NS_MachineGunMuzzle_Batch</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_Batch_Reduced.NS_MachineGunMuzzle_Batch_Reduced</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/CommanderWeapons/NS_MachineGunMuzzle_Batch_Minimal.NS_MachineGunMuzzle_Batch_Minimal</t>
   </si>
 </sst>
 </file>
@@ -909,6 +999,21 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -932,6 +1037,21 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -955,6 +1075,21 @@
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -1036,7 +1171,7 @@
         <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1059,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1069,6 +1204,21 @@
       </c>
       <c r="G8">
         <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" t="s">
+        <v>196</v>
+      </c>
+      <c r="K8" t="s">
+        <v>197</v>
+      </c>
+      <c r="L8" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -1769,10 +1919,10 @@
         <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -1818,7 +1968,7 @@
         <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="E41">
         <v>0.3</v>
@@ -1979,7 +2129,7 @@
         <v>148</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2140,7 +2290,7 @@
         <v>178</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -2149,6 +2299,44 @@
         <v>1</v>
       </c>
       <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>201</v>
+      </c>
+      <c r="I55" t="s">
+        <v>202</v>
+      </c>
+      <c r="J55" t="s">
+        <v>206</v>
+      </c>
+      <c r="K55" t="s">
+        <v>207</v>
+      </c>
+      <c r="L55" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" t="s">
+        <v>205</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
         <v>1</v>
       </c>
     </row>
